--- a/output/roomself_excel/13442.xlsx
+++ b/output/roomself_excel/13442.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>144203</v>
+        <v>70756</v>
       </c>
       <c r="D2" t="n">
-        <v>3088</v>
+        <v>2128</v>
       </c>
       <c r="E2" t="n">
-        <v>473</v>
+        <v>266</v>
       </c>
       <c r="F2" t="n">
-        <v>385</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
@@ -492,16 +492,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>366058</v>
+        <v>253464</v>
       </c>
       <c r="D3" t="n">
-        <v>7304</v>
+        <v>4972</v>
       </c>
       <c r="E3" t="n">
-        <v>905</v>
+        <v>685</v>
       </c>
       <c r="F3" t="n">
-        <v>620</v>
+        <v>463</v>
       </c>
     </row>
     <row r="4">
@@ -514,16 +514,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>71285</v>
+        <v>144203</v>
       </c>
       <c r="D4" t="n">
-        <v>2136</v>
+        <v>3088</v>
       </c>
       <c r="E4" t="n">
-        <v>265</v>
+        <v>473</v>
       </c>
       <c r="F4" t="n">
-        <v>43</v>
+        <v>385</v>
       </c>
     </row>
     <row r="5">
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>48074</v>
+        <v>71285</v>
       </c>
       <c r="D5" t="n">
-        <v>1860</v>
+        <v>2136</v>
       </c>
       <c r="E5" t="n">
-        <v>312</v>
+        <v>265</v>
       </c>
       <c r="F5" t="n">
-        <v>221</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6">
@@ -554,19 +554,63 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>Bath</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>48074</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1860</v>
+      </c>
+      <c r="E6" t="n">
+        <v>312</v>
+      </c>
+      <c r="F6" t="n">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Hallway</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>41838</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1676</v>
+      </c>
+      <c r="E7" t="n">
+        <v>198</v>
+      </c>
+      <c r="F7" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>Storage</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="C8" t="n">
         <v>19095</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D8" t="n">
         <v>1184</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E8" t="n">
         <v>220</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F8" t="n">
         <v>120</v>
       </c>
     </row>

--- a/output/roomself_excel/13442.xlsx
+++ b/output/roomself_excel/13442.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,47 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_3</t>
         </is>
       </c>
     </row>
@@ -475,12 +510,31 @@
       <c r="D2" t="n">
         <v>2128</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
         <v>266</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>266</v>
+      </c>
+      <c r="J2" t="n">
         <v>21</v>
       </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,12 +551,31 @@
       <c r="D3" t="n">
         <v>4972</v>
       </c>
-      <c r="E3" t="n">
-        <v>685</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F3" t="n">
         <v>463</v>
       </c>
+      <c r="G3" t="n">
+        <v>43</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>338</v>
+      </c>
+      <c r="J3" t="n">
+        <v>40</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,12 +592,31 @@
       <c r="D4" t="n">
         <v>3088</v>
       </c>
-      <c r="E4" t="n">
-        <v>473</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>385</v>
-      </c>
+        <v>374</v>
+      </c>
+      <c r="G4" t="n">
+        <v>43</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>342</v>
+      </c>
+      <c r="J4" t="n">
+        <v>43</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,12 +633,23 @@
       <c r="D5" t="n">
         <v>2136</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
         <v>265</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>43</v>
       </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,11 +666,38 @@
       <c r="D6" t="n">
         <v>1860</v>
       </c>
-      <c r="E6" t="n">
-        <v>312</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F6" t="n">
-        <v>221</v>
+        <v>49</v>
+      </c>
+      <c r="G6" t="n">
+        <v>38</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>142</v>
+      </c>
+      <c r="J6" t="n">
+        <v>68</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>244</v>
+      </c>
+      <c r="M6" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="7">
@@ -585,12 +715,23 @@
       <c r="D7" t="n">
         <v>1676</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
         <v>198</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>19</v>
       </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +748,31 @@
       <c r="D8" t="n">
         <v>1184</v>
       </c>
-      <c r="E8" t="n">
-        <v>220</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F8" t="n">
-        <v>120</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="G8" t="n">
+        <v>25</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>95</v>
+      </c>
+      <c r="J8" t="n">
+        <v>19</v>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
